--- a/m2/exemplos/health-check-loja/insumo-health-check-iguatemi.xlsx
+++ b/m2/exemplos/health-check-loja/insumo-health-check-iguatemi.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Health check · 30 dias" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contexto qualitativo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 · Métricas x benchmark" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 · Contexto qualitativo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 · Série diária 30 dias" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,6 +85,12 @@
       <color rgb="006B2E7A"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0087867F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -143,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,6 +181,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1211,4 +1225,1241 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Série diária · Julho/2026 (31 dias)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Base pra você identificar tendência, sazonalidade semanal e efeito dos eventos (reforma, saídas, novo produto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Ticket médio</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Clientes/dia</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Cupuaçu (unid)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Sorbet (unid)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Nota Google (rolling)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Absent. (pessoas)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Reclamações</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>4,40</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>R$ 21,85</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>202</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>4,39</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>R$ 21,70</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>206</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>63</v>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>4,38</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>R$ 6.075</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>R$ 21,43</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>282</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>85</v>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>4,37</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>R$ 6.075</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>R$ 21,24</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>286</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>86</v>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>4,36</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>R$ 21,05</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>215</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>4,35</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 20,86</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>218</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>4,34</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>R$ 20,67</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>221</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>4,33</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>R$ 20,48</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>224</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>4,32</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>R$ 20,29</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>227</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>4,31</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>R$ 6.075</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>R$ 20,10</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>310</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>4,30</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>R$ 3.645</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>R$ 19,91</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>188</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>4,29</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 2.700</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 19,72</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>141</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>4,28</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 2.700</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 19,53</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>143</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>4,27</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>R$ 2.700</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>R$ 19,34</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>145</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>4,26</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>R$ 2.700</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>R$ 19,15</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>147</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>4,25</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 2.700</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 18,96</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>148</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>4,24</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 3.645</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 18,77</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>203</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>4,23</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>R$ 3.645</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>R$ 18,58</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>205</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>59</v>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>4,22</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 18,39</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>257</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>4,21</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>R$ 18,20</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>260</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>78</v>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>4,20</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>R$ 18,01</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>263</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>79</v>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>4,19</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>R$ 17,82</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>266</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>4,18</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>R$ 17,63</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>269</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>81</v>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>4,17</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>R$ 5.164</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>R$ 17,44</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>312</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>96</v>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>R$ 5.164</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>R$ 17,25</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>315</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>R$ 3.825</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>R$ 17,06</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>236</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>4,12</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>R$ 16,87</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>281</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>85</v>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>4,11</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>R$ 16,68</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>284</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>86</v>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>4,10</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>R$ 16,49</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>287</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>4,09</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>R$ 4.500</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>R$ 16,30</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>290</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>88</v>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>4,08</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>